--- a/config/client_template_software.xlsx
+++ b/config/client_template_software.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\CFD-Finance\Reportsradar\Software\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeetendrajaiswal/Desktop/self/poc/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A9D8CB-1797-4CD2-AD5C-7F5F1B508E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B004AE0F-5418-564C-8164-E7171EDAF59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{393B6FBC-BF0F-4967-B316-529553DBBC3B}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="16700" activeTab="5" xr2:uid="{393B6FBC-BF0F-4967-B316-529553DBBC3B}"/>
   </bookViews>
   <sheets>
     <sheet name="Income Statement - Standalone" sheetId="2" r:id="rId1"/>
@@ -1370,9 +1370,6 @@
     <t>=C120+C121+C122</t>
   </si>
   <si>
-    <t>=C124+C125+C126+C127+C128+C129+C130+C130+C131+C132+C133+C134+C135+C136+C137+C138+C139+C140+C141+C142+C143+C144+C145+C146+C147+C148+C149+C150+C151</t>
-  </si>
-  <si>
     <t>=C152+C153+C154</t>
   </si>
   <si>
@@ -1566,6 +1563,9 @@
   </si>
   <si>
     <t>=C93/C8*100</t>
+  </si>
+  <si>
+    <t>=C124+C125+C126+C127+C128+C129+C130+C131+C132+C133+C134+C135+C136+C137+C138+C139+C140+C141+C142+C143+C144+C145+C146+C147+C148+C149+C150+C151</t>
   </si>
 </sst>
 </file>
@@ -1706,8 +1706,8 @@
 <volTypes xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <volType type="realTimeData">
     <main first="mlrtd.rtdfunctions">
-      <tp>
-        <v>2005321363</v>
+      <tp t="e">
+        <v>#N/A</v>
         <stp/>
         <stp>Price</stp>
         <stp>USERID.UMS</stp>
@@ -2037,18 +2037,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66D7CCA8-A49B-485D-B88B-ED86F2FEE801}">
   <dimension ref="A1:H114"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="80.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="80.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2068,13 +2068,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -2096,7 +2096,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -2118,7 +2118,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -2164,7 +2164,7 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2186,7 +2186,7 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2208,7 +2208,7 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
@@ -2254,7 +2254,7 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
@@ -2276,7 +2276,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
@@ -2298,7 +2298,7 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>6</v>
       </c>
@@ -2320,7 +2320,7 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>6</v>
       </c>
@@ -2342,7 +2342,7 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>6</v>
       </c>
@@ -2364,7 +2364,7 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>6</v>
       </c>
@@ -2386,7 +2386,7 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>6</v>
       </c>
@@ -2408,7 +2408,7 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>6</v>
       </c>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>6</v>
       </c>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="H18" s="5"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -2478,7 +2478,7 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>6</v>
       </c>
@@ -2500,7 +2500,7 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>6</v>
       </c>
@@ -2522,7 +2522,7 @@
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>6</v>
       </c>
@@ -2544,7 +2544,7 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>6</v>
       </c>
@@ -2566,7 +2566,7 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>6</v>
       </c>
@@ -2588,7 +2588,7 @@
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>6</v>
       </c>
@@ -2610,7 +2610,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>6</v>
       </c>
@@ -2632,7 +2632,7 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>6</v>
       </c>
@@ -2654,7 +2654,7 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>6</v>
       </c>
@@ -2676,7 +2676,7 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -2698,7 +2698,7 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -2720,7 +2720,7 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -2742,7 +2742,7 @@
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>6</v>
       </c>
@@ -2764,7 +2764,7 @@
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>6</v>
       </c>
@@ -2786,7 +2786,7 @@
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>6</v>
       </c>
@@ -2808,7 +2808,7 @@
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>6</v>
       </c>
@@ -2830,7 +2830,7 @@
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>6</v>
       </c>
@@ -2852,7 +2852,7 @@
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>6</v>
       </c>
@@ -2874,7 +2874,7 @@
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>6</v>
       </c>
@@ -2896,7 +2896,7 @@
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>6</v>
       </c>
@@ -2918,7 +2918,7 @@
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>6</v>
       </c>
@@ -2940,7 +2940,7 @@
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>6</v>
       </c>
@@ -2962,7 +2962,7 @@
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>6</v>
       </c>
@@ -2984,7 +2984,7 @@
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
-    <row r="43" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="13" t="s">
         <v>6</v>
       </c>
@@ -3004,11 +3004,11 @@
         <v>45</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H43" s="13"/>
     </row>
-    <row r="44" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>6</v>
       </c>
@@ -3028,11 +3028,11 @@
         <v>46</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H44" s="5"/>
     </row>
-    <row r="45" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>6</v>
       </c>
@@ -3052,11 +3052,11 @@
         <v>47</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H45" s="5"/>
     </row>
-    <row r="46" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>6</v>
       </c>
@@ -3076,11 +3076,11 @@
         <v>48</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H46" s="5"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>6</v>
       </c>
@@ -3102,7 +3102,7 @@
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>6</v>
       </c>
@@ -3124,7 +3124,7 @@
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>6</v>
       </c>
@@ -3146,7 +3146,7 @@
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>6</v>
       </c>
@@ -3168,7 +3168,7 @@
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>6</v>
       </c>
@@ -3190,7 +3190,7 @@
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>6</v>
       </c>
@@ -3212,7 +3212,7 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>6</v>
       </c>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="H53" s="5"/>
     </row>
-    <row r="54" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>6</v>
       </c>
@@ -3256,11 +3256,11 @@
         <v>57</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H54" s="5"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>6</v>
       </c>
@@ -3282,7 +3282,7 @@
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>6</v>
       </c>
@@ -3304,7 +3304,7 @@
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
     </row>
-    <row r="57" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
         <v>6</v>
       </c>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="H57" s="5"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>6</v>
       </c>
@@ -3350,7 +3350,7 @@
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
     </row>
-    <row r="59" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>6</v>
       </c>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="H59" s="5"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>6</v>
       </c>
@@ -3396,7 +3396,7 @@
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>6</v>
       </c>
@@ -3418,7 +3418,7 @@
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
     </row>
-    <row r="62" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>6</v>
       </c>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="H62" s="5"/>
     </row>
-    <row r="63" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>6</v>
       </c>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="H63" s="5"/>
     </row>
-    <row r="64" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>6</v>
       </c>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="H64" s="5"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>6</v>
       </c>
@@ -3512,7 +3512,7 @@
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>6</v>
       </c>
@@ -3534,7 +3534,7 @@
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>6</v>
       </c>
@@ -3556,7 +3556,7 @@
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>6</v>
       </c>
@@ -3578,7 +3578,7 @@
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
     </row>
-    <row r="69" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>6</v>
       </c>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H69" s="5"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>6</v>
       </c>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H70" s="4"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>6</v>
       </c>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="H71" s="4"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>6</v>
       </c>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="H72" s="4"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>6</v>
       </c>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="H73" s="4"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>6</v>
       </c>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="H74" s="4"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>6</v>
       </c>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="H75" s="4"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>6</v>
       </c>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="H76" s="4"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>6</v>
       </c>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="H77" s="4"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>6</v>
       </c>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="H78" s="4"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>6</v>
       </c>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="H79" s="4"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>6</v>
       </c>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="H80" s="4"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>6</v>
       </c>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="H81" s="4"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>6</v>
       </c>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="H82" s="4"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>6</v>
       </c>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="H83" s="4"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>6</v>
       </c>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="H84" s="4"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>6</v>
       </c>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="H85" s="4"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>6</v>
       </c>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="H86" s="4"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>6</v>
       </c>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="H87" s="4"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>6</v>
       </c>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="H88" s="4"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>6</v>
       </c>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="H89" s="4"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>6</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>6</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>6</v>
       </c>
@@ -4154,11 +4154,11 @@
         <v>100</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H92" s="5"/>
     </row>
-    <row r="93" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A93" s="15" t="s">
         <v>6</v>
       </c>
@@ -4178,11 +4178,11 @@
         <v>101</v>
       </c>
       <c r="G93" s="16" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H93" s="15"/>
     </row>
-    <row r="94" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>6</v>
       </c>
@@ -4202,11 +4202,11 @@
         <v>102</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H94" s="5"/>
     </row>
-    <row r="95" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
         <v>6</v>
       </c>
@@ -4226,11 +4226,11 @@
         <v>103</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H95" s="5"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="15" t="s">
         <v>6</v>
       </c>
@@ -4250,11 +4250,11 @@
         <v>104</v>
       </c>
       <c r="G96" s="16" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H96" s="15"/>
     </row>
-    <row r="97" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
         <v>6</v>
       </c>
@@ -4274,11 +4274,11 @@
         <v>105</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H97" s="5"/>
     </row>
-    <row r="98" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
         <v>6</v>
       </c>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="H98" s="5"/>
     </row>
-    <row r="99" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
         <v>6</v>
       </c>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H99" s="5"/>
     </row>
-    <row r="100" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
         <v>6</v>
       </c>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="H100" s="5"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>6</v>
       </c>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="H101" s="4"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>6</v>
       </c>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H102" s="4"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>6</v>
       </c>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="H103" s="4"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>6</v>
       </c>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="H104" s="4"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>6</v>
       </c>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="H105" s="4"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>6</v>
       </c>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="H106" s="4"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>6</v>
       </c>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H107" s="4"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>6</v>
       </c>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="H108" s="4"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>6</v>
       </c>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H109" s="4"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>6</v>
       </c>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="H110" s="4"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>6</v>
       </c>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="H111" s="4"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
         <v>6</v>
       </c>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="H112" s="4"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
         <v>6</v>
       </c>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="H113" s="4"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
         <v>6</v>
       </c>
@@ -4697,18 +4697,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90FE84ED-F60F-4383-9FBB-69C41DA8C69D}">
   <dimension ref="A1:H130"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="97.42578125" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="97.5" customWidth="1"/>
+    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4728,13 +4728,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -4756,7 +4756,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -4778,7 +4778,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -4824,7 +4824,7 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4846,7 +4846,7 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4868,7 +4868,7 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="H8" s="5"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
@@ -4914,7 +4914,7 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
@@ -4936,7 +4936,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
@@ -4958,7 +4958,7 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>6</v>
       </c>
@@ -4980,7 +4980,7 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>6</v>
       </c>
@@ -5002,7 +5002,7 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>6</v>
       </c>
@@ -5024,7 +5024,7 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>6</v>
       </c>
@@ -5046,7 +5046,7 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>6</v>
       </c>
@@ -5068,7 +5068,7 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>6</v>
       </c>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>6</v>
       </c>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="H18" s="5"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -5138,7 +5138,7 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>6</v>
       </c>
@@ -5160,7 +5160,7 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>6</v>
       </c>
@@ -5182,7 +5182,7 @@
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>6</v>
       </c>
@@ -5204,7 +5204,7 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>6</v>
       </c>
@@ -5226,7 +5226,7 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>6</v>
       </c>
@@ -5248,7 +5248,7 @@
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>6</v>
       </c>
@@ -5270,7 +5270,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>6</v>
       </c>
@@ -5292,7 +5292,7 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>6</v>
       </c>
@@ -5314,7 +5314,7 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>6</v>
       </c>
@@ -5336,7 +5336,7 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -5358,7 +5358,7 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -5380,7 +5380,7 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -5402,7 +5402,7 @@
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>6</v>
       </c>
@@ -5424,7 +5424,7 @@
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>6</v>
       </c>
@@ -5446,7 +5446,7 @@
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>6</v>
       </c>
@@ -5468,7 +5468,7 @@
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>6</v>
       </c>
@@ -5490,7 +5490,7 @@
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>6</v>
       </c>
@@ -5512,7 +5512,7 @@
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>6</v>
       </c>
@@ -5534,7 +5534,7 @@
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>6</v>
       </c>
@@ -5556,7 +5556,7 @@
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>6</v>
       </c>
@@ -5578,7 +5578,7 @@
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>6</v>
       </c>
@@ -5600,7 +5600,7 @@
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>6</v>
       </c>
@@ -5622,7 +5622,7 @@
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>6</v>
       </c>
@@ -5644,7 +5644,7 @@
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
-    <row r="43" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="13" t="s">
         <v>6</v>
       </c>
@@ -5664,11 +5664,11 @@
         <v>45</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H43" s="13"/>
     </row>
-    <row r="44" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="17" t="s">
         <v>6</v>
       </c>
@@ -5688,11 +5688,11 @@
         <v>46</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H44" s="17"/>
     </row>
-    <row r="45" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="17" t="s">
         <v>6</v>
       </c>
@@ -5712,11 +5712,11 @@
         <v>47</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H45" s="17"/>
     </row>
-    <row r="46" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="17" t="s">
         <v>6</v>
       </c>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="H46" s="17"/>
     </row>
-    <row r="47" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="13" t="s">
         <v>6</v>
       </c>
@@ -5760,11 +5760,11 @@
         <v>49</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H47" s="13"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>6</v>
       </c>
@@ -5786,7 +5786,7 @@
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>6</v>
       </c>
@@ -5808,7 +5808,7 @@
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>6</v>
       </c>
@@ -5830,7 +5830,7 @@
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>6</v>
       </c>
@@ -5852,7 +5852,7 @@
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>6</v>
       </c>
@@ -5874,7 +5874,7 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>6</v>
       </c>
@@ -5896,7 +5896,7 @@
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
     </row>
-    <row r="54" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>6</v>
       </c>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="H54" s="5"/>
     </row>
-    <row r="55" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>6</v>
       </c>
@@ -5940,11 +5940,11 @@
         <v>58</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H55" s="5"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>6</v>
       </c>
@@ -5966,7 +5966,7 @@
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>6</v>
       </c>
@@ -5988,7 +5988,7 @@
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
     </row>
-    <row r="58" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
         <v>6</v>
       </c>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="H58" s="5"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>6</v>
       </c>
@@ -6034,7 +6034,7 @@
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
     </row>
-    <row r="60" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
         <v>6</v>
       </c>
@@ -6054,11 +6054,11 @@
         <v>63</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H60" s="5"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>6</v>
       </c>
@@ -6080,7 +6080,7 @@
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>6</v>
       </c>
@@ -6102,7 +6102,7 @@
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
     </row>
-    <row r="63" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>6</v>
       </c>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H63" s="5"/>
     </row>
-    <row r="64" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>6</v>
       </c>
@@ -6146,11 +6146,11 @@
         <v>67</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H64" s="5"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>6</v>
       </c>
@@ -6172,7 +6172,7 @@
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>6</v>
       </c>
@@ -6194,7 +6194,7 @@
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
     </row>
-    <row r="67" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>6</v>
       </c>
@@ -6214,11 +6214,11 @@
         <v>70</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H67" s="5"/>
     </row>
-    <row r="68" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>6</v>
       </c>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H68" s="5"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>6</v>
       </c>
@@ -6264,7 +6264,7 @@
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>6</v>
       </c>
@@ -6286,7 +6286,7 @@
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>6</v>
       </c>
@@ -6308,7 +6308,7 @@
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>6</v>
       </c>
@@ -6330,7 +6330,7 @@
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
     </row>
-    <row r="73" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
         <v>6</v>
       </c>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="H73" s="5"/>
     </row>
-    <row r="74" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
         <v>6</v>
       </c>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="H74" s="5"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>6</v>
       </c>
@@ -6400,7 +6400,7 @@
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>6</v>
       </c>
@@ -6422,7 +6422,7 @@
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
     </row>
-    <row r="77" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>6</v>
       </c>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="H77" s="5"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>6</v>
       </c>
@@ -6468,7 +6468,7 @@
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>6</v>
       </c>
@@ -6490,7 +6490,7 @@
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
     </row>
-    <row r="80" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
         <v>6</v>
       </c>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="H80" s="5"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>6</v>
       </c>
@@ -6536,7 +6536,7 @@
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>6</v>
       </c>
@@ -6558,7 +6558,7 @@
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>6</v>
       </c>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="H83" s="4"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>6</v>
       </c>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="H84" s="4"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>6</v>
       </c>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="H85" s="4"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>6</v>
       </c>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="H86" s="4"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>6</v>
       </c>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="H87" s="4"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>6</v>
       </c>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H88" s="4"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>6</v>
       </c>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="H89" s="4"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>6</v>
       </c>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="H90" s="4"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>6</v>
       </c>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="H91" s="4"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>6</v>
       </c>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="H92" s="4"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>6</v>
       </c>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="H93" s="4"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>6</v>
       </c>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="H94" s="4"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>6</v>
       </c>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="H95" s="4"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>6</v>
       </c>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="H96" s="4"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>6</v>
       </c>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="H97" s="4"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>6</v>
       </c>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="H98" s="4"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>6</v>
       </c>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="H99" s="4"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>6</v>
       </c>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="H100" s="4"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>6</v>
       </c>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="H101" s="4"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>6</v>
       </c>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="H102" s="4"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>6</v>
       </c>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="H103" s="4"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>6</v>
       </c>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="H104" s="4"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>6</v>
       </c>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="H105" s="4"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>6</v>
       </c>
@@ -7136,7 +7136,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>6</v>
       </c>
@@ -7162,7 +7162,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="108" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
         <v>6</v>
       </c>
@@ -7182,11 +7182,11 @@
         <v>116</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H108" s="5"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="15" t="s">
         <v>6</v>
       </c>
@@ -7206,11 +7206,11 @@
         <v>117</v>
       </c>
       <c r="G109" s="16" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H109" s="15"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>6</v>
       </c>
@@ -7230,11 +7230,11 @@
         <v>118</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H110" s="5"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>6</v>
       </c>
@@ -7254,11 +7254,11 @@
         <v>119</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H111" s="5"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="15" t="s">
         <v>6</v>
       </c>
@@ -7278,11 +7278,11 @@
         <v>120</v>
       </c>
       <c r="G112" s="16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H112" s="15"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
         <v>6</v>
       </c>
@@ -7302,11 +7302,11 @@
         <v>121</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H113" s="5"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
         <v>6</v>
       </c>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="H114" s="5"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
         <v>6</v>
       </c>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="H115" s="5"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
         <v>6</v>
       </c>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="H116" s="5"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
         <v>6</v>
       </c>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="H117" s="4"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
         <v>6</v>
       </c>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="H118" s="4"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
         <v>6</v>
       </c>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="H119" s="4"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
         <v>6</v>
       </c>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="H120" s="4"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
         <v>6</v>
       </c>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="H121" s="4"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
         <v>6</v>
       </c>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="H122" s="4"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
         <v>6</v>
       </c>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="H123" s="4"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
         <v>6</v>
       </c>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="H124" s="4"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
         <v>6</v>
       </c>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="H125" s="4"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
         <v>6</v>
       </c>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="H126" s="4"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
         <v>6</v>
       </c>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="H127" s="4"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
         <v>6</v>
       </c>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="H128" s="4"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
         <v>6</v>
       </c>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H129" s="4"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
         <v>6</v>
       </c>
@@ -7722,12 +7722,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21F2CBF1-32EC-46FC-93C1-9E3122CDE9F9}">
   <dimension ref="A50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" t="e">
         <f>RTD("mlrtd.rtdfunctions",,"Price","USERID.UMS","Last")</f>
-        <v>2005321363</v>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -7738,18 +7738,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F342ECA-2AC5-4F20-81B1-FDF9922073BB}">
   <dimension ref="A1:H78"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.28515625" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" customWidth="1"/>
+    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7769,13 +7769,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -7799,7 +7799,7 @@
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -7821,7 +7821,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -7843,7 +7843,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -7865,7 +7865,7 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -7887,7 +7887,7 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="H7" s="5"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -7933,7 +7933,7 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
@@ -7955,7 +7955,7 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
@@ -7977,7 +7977,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
@@ -7999,7 +7999,7 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>6</v>
       </c>
@@ -8021,7 +8021,7 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>6</v>
       </c>
@@ -8043,7 +8043,7 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>6</v>
       </c>
@@ -8065,7 +8065,7 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>6</v>
       </c>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>6</v>
       </c>
@@ -8111,7 +8111,7 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
@@ -8133,7 +8133,7 @@
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
@@ -8155,7 +8155,7 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>6</v>
       </c>
@@ -8175,11 +8175,11 @@
         <v>23</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>6</v>
       </c>
@@ -8201,7 +8201,7 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>6</v>
       </c>
@@ -8223,7 +8223,7 @@
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>6</v>
       </c>
@@ -8245,7 +8245,7 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>6</v>
       </c>
@@ -8267,7 +8267,7 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>6</v>
       </c>
@@ -8289,7 +8289,7 @@
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>6</v>
       </c>
@@ -8309,11 +8309,11 @@
         <v>29</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H25" s="5"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>6</v>
       </c>
@@ -8335,7 +8335,7 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>6</v>
       </c>
@@ -8357,7 +8357,7 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8379,7 +8379,7 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -8401,7 +8401,7 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -8423,7 +8423,7 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>6</v>
       </c>
@@ -8443,11 +8443,11 @@
         <v>37</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H31" s="5"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>6</v>
       </c>
@@ -8469,7 +8469,7 @@
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>6</v>
       </c>
@@ -8491,7 +8491,7 @@
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>6</v>
       </c>
@@ -8513,7 +8513,7 @@
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>6</v>
       </c>
@@ -8535,7 +8535,7 @@
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>6</v>
       </c>
@@ -8557,7 +8557,7 @@
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>6</v>
       </c>
@@ -8579,7 +8579,7 @@
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>6</v>
       </c>
@@ -8599,11 +8599,11 @@
         <v>44</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H38" s="5"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>6</v>
       </c>
@@ -8625,7 +8625,7 @@
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>6</v>
       </c>
@@ -8647,7 +8647,7 @@
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="13" t="s">
         <v>6</v>
       </c>
@@ -8667,11 +8667,11 @@
         <v>47</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H41" s="13"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>6</v>
       </c>
@@ -8693,7 +8693,7 @@
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>6</v>
       </c>
@@ -8715,7 +8715,7 @@
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>6</v>
       </c>
@@ -8737,7 +8737,7 @@
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
     </row>
-    <row r="45" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>6</v>
       </c>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="H45" s="5"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>6</v>
       </c>
@@ -8783,7 +8783,7 @@
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>6</v>
       </c>
@@ -8805,7 +8805,7 @@
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
     </row>
-    <row r="48" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>6</v>
       </c>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="H48" s="5"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>6</v>
       </c>
@@ -8851,7 +8851,7 @@
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>6</v>
       </c>
@@ -8873,7 +8873,7 @@
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>6</v>
       </c>
@@ -8895,7 +8895,7 @@
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>6</v>
       </c>
@@ -8917,7 +8917,7 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>6</v>
       </c>
@@ -8939,7 +8939,7 @@
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>6</v>
       </c>
@@ -8961,7 +8961,7 @@
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
     </row>
-    <row r="55" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>6</v>
       </c>
@@ -8985,7 +8985,7 @@
       </c>
       <c r="H55" s="5"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>6</v>
       </c>
@@ -9007,7 +9007,7 @@
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>6</v>
       </c>
@@ -9029,7 +9029,7 @@
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>6</v>
       </c>
@@ -9051,7 +9051,7 @@
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>6</v>
       </c>
@@ -9073,7 +9073,7 @@
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>6</v>
       </c>
@@ -9095,7 +9095,7 @@
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
     </row>
-    <row r="61" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
         <v>6</v>
       </c>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="H61" s="5"/>
     </row>
-    <row r="62" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>6</v>
       </c>
@@ -9143,7 +9143,7 @@
       </c>
       <c r="H62" s="5"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>6</v>
       </c>
@@ -9165,7 +9165,7 @@
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>6</v>
       </c>
@@ -9187,7 +9187,7 @@
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>6</v>
       </c>
@@ -9209,7 +9209,7 @@
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>6</v>
       </c>
@@ -9231,7 +9231,7 @@
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>6</v>
       </c>
@@ -9253,7 +9253,7 @@
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>6</v>
       </c>
@@ -9275,7 +9275,7 @@
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>6</v>
       </c>
@@ -9297,7 +9297,7 @@
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>6</v>
       </c>
@@ -9319,7 +9319,7 @@
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>6</v>
       </c>
@@ -9341,7 +9341,7 @@
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
     </row>
-    <row r="72" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
         <v>6</v>
       </c>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="H72" s="5"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>6</v>
       </c>
@@ -9387,7 +9387,7 @@
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>6</v>
       </c>
@@ -9409,7 +9409,7 @@
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
     </row>
-    <row r="75" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
         <v>6</v>
       </c>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="H75" s="5"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>6</v>
       </c>
@@ -9455,7 +9455,7 @@
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>6</v>
       </c>
@@ -9477,7 +9477,7 @@
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
     </row>
-    <row r="78" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="13" t="s">
         <v>6</v>
       </c>
@@ -9497,7 +9497,7 @@
         <v>93</v>
       </c>
       <c r="G78" s="20" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H78" s="13"/>
     </row>
@@ -9509,19 +9509,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92951EEB-C89D-4C40-BAF8-E13C83621749}">
   <dimension ref="A1:H80"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.28515625" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.33203125" customWidth="1"/>
+    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.140625" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.1640625" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9541,13 +9541,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -9593,7 +9593,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -9615,7 +9615,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -9637,7 +9637,7 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -9659,7 +9659,7 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="H7" s="5"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -9705,7 +9705,7 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
@@ -9727,7 +9727,7 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
@@ -9749,7 +9749,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
@@ -9771,7 +9771,7 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>6</v>
       </c>
@@ -9793,7 +9793,7 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>6</v>
       </c>
@@ -9815,7 +9815,7 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>6</v>
       </c>
@@ -9837,7 +9837,7 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>6</v>
       </c>
@@ -9859,7 +9859,7 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>6</v>
       </c>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
@@ -9905,7 +9905,7 @@
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
@@ -9927,7 +9927,7 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -9949,7 +9949,7 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>6</v>
       </c>
@@ -9969,11 +9969,11 @@
         <v>24</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>6</v>
       </c>
@@ -9995,7 +9995,7 @@
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>6</v>
       </c>
@@ -10017,7 +10017,7 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>6</v>
       </c>
@@ -10039,7 +10039,7 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>6</v>
       </c>
@@ -10061,7 +10061,7 @@
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>6</v>
       </c>
@@ -10083,7 +10083,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>6</v>
       </c>
@@ -10103,11 +10103,11 @@
         <v>30</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>6</v>
       </c>
@@ -10129,7 +10129,7 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>6</v>
       </c>
@@ -10151,7 +10151,7 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -10173,7 +10173,7 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -10195,7 +10195,7 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -10217,7 +10217,7 @@
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" s="7" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>6</v>
       </c>
@@ -10237,11 +10237,11 @@
         <v>38</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H32" s="5"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>6</v>
       </c>
@@ -10263,7 +10263,7 @@
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>6</v>
       </c>
@@ -10285,7 +10285,7 @@
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>6</v>
       </c>
@@ -10307,7 +10307,7 @@
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>6</v>
       </c>
@@ -10329,7 +10329,7 @@
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>6</v>
       </c>
@@ -10351,7 +10351,7 @@
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>6</v>
       </c>
@@ -10373,7 +10373,7 @@
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>6</v>
       </c>
@@ -10393,11 +10393,11 @@
         <v>45</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H39" s="5"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>6</v>
       </c>
@@ -10419,7 +10419,7 @@
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>6</v>
       </c>
@@ -10441,7 +10441,7 @@
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
-    <row r="42" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="15" t="s">
         <v>6</v>
       </c>
@@ -10461,11 +10461,11 @@
         <v>48</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H42" s="15"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>6</v>
       </c>
@@ -10487,7 +10487,7 @@
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>6</v>
       </c>
@@ -10509,7 +10509,7 @@
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>6</v>
       </c>
@@ -10531,7 +10531,7 @@
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
     </row>
-    <row r="46" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>6</v>
       </c>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="H46" s="5"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>6</v>
       </c>
@@ -10577,7 +10577,7 @@
       <c r="G47" s="4"/>
       <c r="H47" s="5"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>6</v>
       </c>
@@ -10599,7 +10599,7 @@
       <c r="G48" s="4"/>
       <c r="H48" s="5"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>6</v>
       </c>
@@ -10621,7 +10621,7 @@
       <c r="G49" s="4"/>
       <c r="H49" s="5"/>
     </row>
-    <row r="50" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>6</v>
       </c>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="H50" s="5"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>6</v>
       </c>
@@ -10667,7 +10667,7 @@
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>6</v>
       </c>
@@ -10689,7 +10689,7 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>6</v>
       </c>
@@ -10711,7 +10711,7 @@
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>6</v>
       </c>
@@ -10733,7 +10733,7 @@
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>6</v>
       </c>
@@ -10755,7 +10755,7 @@
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>6</v>
       </c>
@@ -10777,7 +10777,7 @@
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
     </row>
-    <row r="57" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
         <v>6</v>
       </c>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="H57" s="5"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>6</v>
       </c>
@@ -10823,7 +10823,7 @@
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>6</v>
       </c>
@@ -10845,7 +10845,7 @@
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>6</v>
       </c>
@@ -10867,7 +10867,7 @@
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>6</v>
       </c>
@@ -10889,7 +10889,7 @@
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>6</v>
       </c>
@@ -10911,7 +10911,7 @@
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
     </row>
-    <row r="63" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>6</v>
       </c>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="H63" s="5"/>
     </row>
-    <row r="64" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>6</v>
       </c>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="H64" s="5"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>6</v>
       </c>
@@ -10981,7 +10981,7 @@
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>6</v>
       </c>
@@ -11003,7 +11003,7 @@
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>6</v>
       </c>
@@ -11025,7 +11025,7 @@
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>6</v>
       </c>
@@ -11047,7 +11047,7 @@
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>6</v>
       </c>
@@ -11071,7 +11071,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>6</v>
       </c>
@@ -11093,7 +11093,7 @@
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>6</v>
       </c>
@@ -11115,7 +11115,7 @@
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>6</v>
       </c>
@@ -11137,7 +11137,7 @@
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>6</v>
       </c>
@@ -11159,7 +11159,7 @@
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
     </row>
-    <row r="74" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
         <v>6</v>
       </c>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="H74" s="5"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>6</v>
       </c>
@@ -11205,7 +11205,7 @@
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>6</v>
       </c>
@@ -11227,7 +11227,7 @@
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
     </row>
-    <row r="77" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>6</v>
       </c>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="H77" s="5"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>6</v>
       </c>
@@ -11273,7 +11273,7 @@
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>6</v>
       </c>
@@ -11295,7 +11295,7 @@
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
     </row>
-    <row r="80" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="13" t="s">
         <v>6</v>
       </c>
@@ -11315,7 +11315,7 @@
         <v>95</v>
       </c>
       <c r="G80" s="14" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H80" s="13"/>
     </row>
@@ -11327,18 +11327,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F32FB8D-3022-456B-99AE-3D1AE8F05CEF}">
   <dimension ref="A1:H162"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="61" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11358,13 +11358,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -11388,7 +11388,7 @@
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -11410,7 +11410,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -11432,7 +11432,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -11454,7 +11454,7 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -11476,7 +11476,7 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -11498,7 +11498,7 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -11520,7 +11520,7 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
@@ -11542,7 +11542,7 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
@@ -11564,7 +11564,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
@@ -11586,7 +11586,7 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>6</v>
       </c>
@@ -11608,7 +11608,7 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>6</v>
       </c>
@@ -11630,7 +11630,7 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>6</v>
       </c>
@@ -11652,7 +11652,7 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>6</v>
       </c>
@@ -11674,7 +11674,7 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>6</v>
       </c>
@@ -11696,7 +11696,7 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
@@ -11718,7 +11718,7 @@
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
@@ -11740,7 +11740,7 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -11762,7 +11762,7 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>6</v>
       </c>
@@ -11784,7 +11784,7 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>6</v>
       </c>
@@ -11806,7 +11806,7 @@
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>6</v>
       </c>
@@ -11828,7 +11828,7 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>6</v>
       </c>
@@ -11850,7 +11850,7 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>6</v>
       </c>
@@ -11872,7 +11872,7 @@
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>6</v>
       </c>
@@ -11894,7 +11894,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>6</v>
       </c>
@@ -11916,7 +11916,7 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>6</v>
       </c>
@@ -11938,7 +11938,7 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>6</v>
       </c>
@@ -11960,7 +11960,7 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -11982,7 +11982,7 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -12004,7 +12004,7 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -12026,7 +12026,7 @@
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>6</v>
       </c>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="H32" s="5"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>6</v>
       </c>
@@ -12072,7 +12072,7 @@
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>6</v>
       </c>
@@ -12094,7 +12094,7 @@
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>6</v>
       </c>
@@ -12116,7 +12116,7 @@
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>6</v>
       </c>
@@ -12138,7 +12138,7 @@
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>6</v>
       </c>
@@ -12160,7 +12160,7 @@
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>6</v>
       </c>
@@ -12182,7 +12182,7 @@
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>6</v>
       </c>
@@ -12204,7 +12204,7 @@
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>6</v>
       </c>
@@ -12226,7 +12226,7 @@
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>6</v>
       </c>
@@ -12248,7 +12248,7 @@
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>6</v>
       </c>
@@ -12270,7 +12270,7 @@
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>6</v>
       </c>
@@ -12292,7 +12292,7 @@
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>6</v>
       </c>
@@ -12314,7 +12314,7 @@
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>6</v>
       </c>
@@ -12336,7 +12336,7 @@
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>6</v>
       </c>
@@ -12358,7 +12358,7 @@
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>6</v>
       </c>
@@ -12380,7 +12380,7 @@
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>6</v>
       </c>
@@ -12402,7 +12402,7 @@
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>6</v>
       </c>
@@ -12424,7 +12424,7 @@
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>6</v>
       </c>
@@ -12446,7 +12446,7 @@
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>6</v>
       </c>
@@ -12468,7 +12468,7 @@
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>6</v>
       </c>
@@ -12490,7 +12490,7 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>6</v>
       </c>
@@ -12512,7 +12512,7 @@
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>6</v>
       </c>
@@ -12534,7 +12534,7 @@
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>6</v>
       </c>
@@ -12556,7 +12556,7 @@
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>6</v>
       </c>
@@ -12578,7 +12578,7 @@
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>6</v>
       </c>
@@ -12600,7 +12600,7 @@
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>6</v>
       </c>
@@ -12622,7 +12622,7 @@
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
     </row>
-    <row r="59" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>6</v>
       </c>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="H59" s="5"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>6</v>
       </c>
@@ -12668,7 +12668,7 @@
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>6</v>
       </c>
@@ -12690,7 +12690,7 @@
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>6</v>
       </c>
@@ -12712,7 +12712,7 @@
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>6</v>
       </c>
@@ -12734,7 +12734,7 @@
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>6</v>
       </c>
@@ -12756,7 +12756,7 @@
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>6</v>
       </c>
@@ -12778,7 +12778,7 @@
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>6</v>
       </c>
@@ -12800,7 +12800,7 @@
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>6</v>
       </c>
@@ -12822,7 +12822,7 @@
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
     </row>
-    <row r="68" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>6</v>
       </c>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="H68" s="5"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>6</v>
       </c>
@@ -12868,7 +12868,7 @@
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>6</v>
       </c>
@@ -12890,7 +12890,7 @@
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>6</v>
       </c>
@@ -12912,7 +12912,7 @@
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>6</v>
       </c>
@@ -12934,7 +12934,7 @@
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>6</v>
       </c>
@@ -12956,7 +12956,7 @@
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>6</v>
       </c>
@@ -12978,7 +12978,7 @@
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>6</v>
       </c>
@@ -13000,7 +13000,7 @@
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>6</v>
       </c>
@@ -13022,7 +13022,7 @@
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>6</v>
       </c>
@@ -13044,7 +13044,7 @@
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
     </row>
-    <row r="78" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
         <v>6</v>
       </c>
@@ -13068,7 +13068,7 @@
       </c>
       <c r="H78" s="5"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>6</v>
       </c>
@@ -13090,7 +13090,7 @@
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>6</v>
       </c>
@@ -13112,7 +13112,7 @@
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>6</v>
       </c>
@@ -13134,7 +13134,7 @@
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>6</v>
       </c>
@@ -13156,7 +13156,7 @@
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>6</v>
       </c>
@@ -13178,7 +13178,7 @@
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>6</v>
       </c>
@@ -13200,7 +13200,7 @@
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>6</v>
       </c>
@@ -13222,7 +13222,7 @@
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>6</v>
       </c>
@@ -13244,7 +13244,7 @@
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>6</v>
       </c>
@@ -13266,7 +13266,7 @@
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>6</v>
       </c>
@@ -13288,7 +13288,7 @@
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>6</v>
       </c>
@@ -13310,7 +13310,7 @@
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>6</v>
       </c>
@@ -13332,7 +13332,7 @@
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>6</v>
       </c>
@@ -13354,7 +13354,7 @@
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>6</v>
       </c>
@@ -13376,7 +13376,7 @@
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>6</v>
       </c>
@@ -13398,7 +13398,7 @@
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>6</v>
       </c>
@@ -13420,7 +13420,7 @@
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>6</v>
       </c>
@@ -13442,7 +13442,7 @@
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>6</v>
       </c>
@@ -13464,7 +13464,7 @@
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>6</v>
       </c>
@@ -13486,7 +13486,7 @@
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>6</v>
       </c>
@@ -13508,7 +13508,7 @@
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>6</v>
       </c>
@@ -13530,7 +13530,7 @@
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>6</v>
       </c>
@@ -13552,7 +13552,7 @@
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>6</v>
       </c>
@@ -13574,7 +13574,7 @@
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>6</v>
       </c>
@@ -13596,7 +13596,7 @@
       <c r="G102" s="4"/>
       <c r="H102" s="4"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>6</v>
       </c>
@@ -13618,7 +13618,7 @@
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>6</v>
       </c>
@@ -13640,7 +13640,7 @@
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>6</v>
       </c>
@@ -13662,7 +13662,7 @@
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>6</v>
       </c>
@@ -13684,7 +13684,7 @@
       <c r="G106" s="4"/>
       <c r="H106" s="4"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>6</v>
       </c>
@@ -13706,7 +13706,7 @@
       <c r="G107" s="4"/>
       <c r="H107" s="4"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>6</v>
       </c>
@@ -13728,7 +13728,7 @@
       <c r="G108" s="4"/>
       <c r="H108" s="4"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>6</v>
       </c>
@@ -13750,7 +13750,7 @@
       <c r="G109" s="4"/>
       <c r="H109" s="4"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>6</v>
       </c>
@@ -13772,7 +13772,7 @@
       <c r="G110" s="4"/>
       <c r="H110" s="4"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>6</v>
       </c>
@@ -13794,7 +13794,7 @@
       <c r="G111" s="4"/>
       <c r="H111" s="4"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
         <v>6</v>
       </c>
@@ -13816,7 +13816,7 @@
       <c r="G112" s="4"/>
       <c r="H112" s="4"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
         <v>6</v>
       </c>
@@ -13838,7 +13838,7 @@
       <c r="G113" s="4"/>
       <c r="H113" s="4"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
         <v>6</v>
       </c>
@@ -13860,7 +13860,7 @@
       <c r="G114" s="4"/>
       <c r="H114" s="4"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
         <v>6</v>
       </c>
@@ -13882,7 +13882,7 @@
       <c r="G115" s="4"/>
       <c r="H115" s="4"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
         <v>6</v>
       </c>
@@ -13904,7 +13904,7 @@
       <c r="G116" s="4"/>
       <c r="H116" s="4"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
         <v>6</v>
       </c>
@@ -13926,7 +13926,7 @@
       <c r="G117" s="4"/>
       <c r="H117" s="4"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
         <v>6</v>
       </c>
@@ -13948,7 +13948,7 @@
       <c r="G118" s="4"/>
       <c r="H118" s="4"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
         <v>6</v>
       </c>
@@ -13970,7 +13970,7 @@
       <c r="G119" s="4"/>
       <c r="H119" s="4"/>
     </row>
-    <row r="120" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
         <v>6</v>
       </c>
@@ -13994,7 +13994,7 @@
       </c>
       <c r="H120" s="5"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
         <v>6</v>
       </c>
@@ -14016,7 +14016,7 @@
       <c r="G121" s="4"/>
       <c r="H121" s="4"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
         <v>6</v>
       </c>
@@ -14038,7 +14038,7 @@
       <c r="G122" s="4"/>
       <c r="H122" s="4"/>
     </row>
-    <row r="123" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
         <v>6</v>
       </c>
@@ -14062,7 +14062,7 @@
       </c>
       <c r="H123" s="5"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
         <v>6</v>
       </c>
@@ -14084,7 +14084,7 @@
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
         <v>6</v>
       </c>
@@ -14106,7 +14106,7 @@
       <c r="G125" s="4"/>
       <c r="H125" s="4"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
         <v>6</v>
       </c>
@@ -14128,7 +14128,7 @@
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
         <v>6</v>
       </c>
@@ -14150,7 +14150,7 @@
       <c r="G127" s="4"/>
       <c r="H127" s="4"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
         <v>6</v>
       </c>
@@ -14172,7 +14172,7 @@
       <c r="G128" s="4"/>
       <c r="H128" s="4"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
         <v>6</v>
       </c>
@@ -14194,7 +14194,7 @@
       <c r="G129" s="4"/>
       <c r="H129" s="4"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
         <v>6</v>
       </c>
@@ -14216,7 +14216,7 @@
       <c r="G130" s="4"/>
       <c r="H130" s="4"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
         <v>6</v>
       </c>
@@ -14238,7 +14238,7 @@
       <c r="G131" s="4"/>
       <c r="H131" s="4"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
         <v>6</v>
       </c>
@@ -14260,7 +14260,7 @@
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
         <v>6</v>
       </c>
@@ -14282,7 +14282,7 @@
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
         <v>6</v>
       </c>
@@ -14304,7 +14304,7 @@
       <c r="G134" s="4"/>
       <c r="H134" s="4"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
         <v>6</v>
       </c>
@@ -14326,7 +14326,7 @@
       <c r="G135" s="4"/>
       <c r="H135" s="4"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
         <v>6</v>
       </c>
@@ -14348,7 +14348,7 @@
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
         <v>6</v>
       </c>
@@ -14370,7 +14370,7 @@
       <c r="G137" s="4"/>
       <c r="H137" s="4"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
         <v>6</v>
       </c>
@@ -14392,7 +14392,7 @@
       <c r="G138" s="4"/>
       <c r="H138" s="4"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>6</v>
       </c>
@@ -14414,7 +14414,7 @@
       <c r="G139" s="4"/>
       <c r="H139" s="4"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
         <v>6</v>
       </c>
@@ -14436,7 +14436,7 @@
       <c r="G140" s="4"/>
       <c r="H140" s="4"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
         <v>6</v>
       </c>
@@ -14458,7 +14458,7 @@
       <c r="G141" s="4"/>
       <c r="H141" s="4"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
         <v>6</v>
       </c>
@@ -14480,7 +14480,7 @@
       <c r="G142" s="4"/>
       <c r="H142" s="4"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
         <v>6</v>
       </c>
@@ -14502,7 +14502,7 @@
       <c r="G143" s="4"/>
       <c r="H143" s="4"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
         <v>6</v>
       </c>
@@ -14524,7 +14524,7 @@
       <c r="G144" s="4"/>
       <c r="H144" s="4"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
         <v>6</v>
       </c>
@@ -14546,7 +14546,7 @@
       <c r="G145" s="4"/>
       <c r="H145" s="4"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
         <v>6</v>
       </c>
@@ -14568,7 +14568,7 @@
       <c r="G146" s="4"/>
       <c r="H146" s="4"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
         <v>6</v>
       </c>
@@ -14590,7 +14590,7 @@
       <c r="G147" s="4"/>
       <c r="H147" s="4"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
         <v>6</v>
       </c>
@@ -14612,7 +14612,7 @@
       <c r="G148" s="4"/>
       <c r="H148" s="4"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
         <v>6</v>
       </c>
@@ -14634,7 +14634,7 @@
       <c r="G149" s="4"/>
       <c r="H149" s="4"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
         <v>6</v>
       </c>
@@ -14656,7 +14656,7 @@
       <c r="G150" s="4"/>
       <c r="H150" s="4"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
         <v>6</v>
       </c>
@@ -14678,7 +14678,7 @@
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
     </row>
-    <row r="152" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A152" s="5" t="s">
         <v>6</v>
       </c>
@@ -14698,11 +14698,11 @@
         <v>156</v>
       </c>
       <c r="G152" s="9" t="s">
-        <v>438</v>
+        <v>503</v>
       </c>
       <c r="H152" s="5"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
         <v>6</v>
       </c>
@@ -14724,7 +14724,7 @@
       <c r="G153" s="4"/>
       <c r="H153" s="4"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
         <v>6</v>
       </c>
@@ -14746,7 +14746,7 @@
       <c r="G154" s="4"/>
       <c r="H154" s="4"/>
     </row>
-    <row r="155" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A155" s="5" t="s">
         <v>6</v>
       </c>
@@ -14766,11 +14766,11 @@
         <v>159</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H155" s="5"/>
     </row>
-    <row r="156" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A156" s="5" t="s">
         <v>6</v>
       </c>
@@ -14790,11 +14790,11 @@
         <v>160</v>
       </c>
       <c r="G156" s="9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H156" s="5"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
         <v>6</v>
       </c>
@@ -14818,7 +14818,7 @@
       </c>
       <c r="H157" s="4"/>
     </row>
-    <row r="158" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A158" s="5" t="s">
         <v>6</v>
       </c>
@@ -14838,11 +14838,11 @@
         <v>162</v>
       </c>
       <c r="G158" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H158" s="5"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
         <v>6</v>
       </c>
@@ -14865,10 +14865,10 @@
         <v>394</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
         <v>6</v>
       </c>
@@ -14892,7 +14892,7 @@
       </c>
       <c r="H160" s="4"/>
     </row>
-    <row r="161" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A161" s="5" t="s">
         <v>6</v>
       </c>
@@ -14912,11 +14912,11 @@
         <v>165</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H161" s="5"/>
     </row>
-    <row r="162" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A162" s="5" t="s">
         <v>6</v>
       </c>
@@ -14948,18 +14948,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D89AC36-F2D2-459A-9C67-E01E2B0FB5C4}">
   <dimension ref="A1:J166"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.5703125" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.5" customWidth="1"/>
+    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14979,13 +14979,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -15009,7 +15009,7 @@
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -15033,7 +15033,7 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -15057,7 +15057,7 @@
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -15081,7 +15081,7 @@
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -15105,7 +15105,7 @@
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -15129,7 +15129,7 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -15153,7 +15153,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
@@ -15177,7 +15177,7 @@
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
@@ -15201,7 +15201,7 @@
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
@@ -15225,7 +15225,7 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>6</v>
       </c>
@@ -15249,7 +15249,7 @@
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>6</v>
       </c>
@@ -15273,7 +15273,7 @@
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>6</v>
       </c>
@@ -15297,7 +15297,7 @@
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>6</v>
       </c>
@@ -15321,7 +15321,7 @@
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>6</v>
       </c>
@@ -15345,7 +15345,7 @@
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
@@ -15369,7 +15369,7 @@
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
@@ -15393,7 +15393,7 @@
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -15417,7 +15417,7 @@
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>6</v>
       </c>
@@ -15441,7 +15441,7 @@
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>6</v>
       </c>
@@ -15465,7 +15465,7 @@
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>6</v>
       </c>
@@ -15489,7 +15489,7 @@
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>6</v>
       </c>
@@ -15513,7 +15513,7 @@
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>6</v>
       </c>
@@ -15537,7 +15537,7 @@
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>6</v>
       </c>
@@ -15561,7 +15561,7 @@
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>6</v>
       </c>
@@ -15585,7 +15585,7 @@
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>6</v>
       </c>
@@ -15609,7 +15609,7 @@
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>6</v>
       </c>
@@ -15633,7 +15633,7 @@
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -15657,7 +15657,7 @@
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -15681,7 +15681,7 @@
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -15705,7 +15705,7 @@
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>6</v>
       </c>
@@ -15729,7 +15729,7 @@
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
     </row>
-    <row r="33" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>6</v>
       </c>
@@ -15749,11 +15749,11 @@
         <v>34</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H33" s="5"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>6</v>
       </c>
@@ -15777,7 +15777,7 @@
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>6</v>
       </c>
@@ -15801,7 +15801,7 @@
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>6</v>
       </c>
@@ -15825,7 +15825,7 @@
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>6</v>
       </c>
@@ -15849,7 +15849,7 @@
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>6</v>
       </c>
@@ -15873,7 +15873,7 @@
       <c r="I38" s="7"/>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>6</v>
       </c>
@@ -15897,7 +15897,7 @@
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>6</v>
       </c>
@@ -15921,7 +15921,7 @@
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>6</v>
       </c>
@@ -15945,7 +15945,7 @@
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>6</v>
       </c>
@@ -15969,7 +15969,7 @@
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>6</v>
       </c>
@@ -15993,7 +15993,7 @@
       <c r="I43" s="7"/>
       <c r="J43" s="7"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>6</v>
       </c>
@@ -16017,7 +16017,7 @@
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>6</v>
       </c>
@@ -16041,7 +16041,7 @@
       <c r="I45" s="7"/>
       <c r="J45" s="7"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>6</v>
       </c>
@@ -16065,7 +16065,7 @@
       <c r="I46" s="7"/>
       <c r="J46" s="7"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>6</v>
       </c>
@@ -16089,7 +16089,7 @@
       <c r="I47" s="7"/>
       <c r="J47" s="7"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>6</v>
       </c>
@@ -16113,7 +16113,7 @@
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>6</v>
       </c>
@@ -16137,7 +16137,7 @@
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>6</v>
       </c>
@@ -16161,7 +16161,7 @@
       <c r="I50" s="7"/>
       <c r="J50" s="7"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>6</v>
       </c>
@@ -16185,7 +16185,7 @@
       <c r="I51" s="7"/>
       <c r="J51" s="7"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>6</v>
       </c>
@@ -16209,7 +16209,7 @@
       <c r="I52" s="7"/>
       <c r="J52" s="7"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>6</v>
       </c>
@@ -16233,7 +16233,7 @@
       <c r="I53" s="7"/>
       <c r="J53" s="7"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>6</v>
       </c>
@@ -16257,7 +16257,7 @@
       <c r="I54" s="7"/>
       <c r="J54" s="7"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>6</v>
       </c>
@@ -16281,7 +16281,7 @@
       <c r="I55" s="7"/>
       <c r="J55" s="7"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>6</v>
       </c>
@@ -16305,7 +16305,7 @@
       <c r="I56" s="7"/>
       <c r="J56" s="7"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>6</v>
       </c>
@@ -16329,7 +16329,7 @@
       <c r="I57" s="7"/>
       <c r="J57" s="7"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>6</v>
       </c>
@@ -16353,7 +16353,7 @@
       <c r="I58" s="7"/>
       <c r="J58" s="7"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>6</v>
       </c>
@@ -16377,7 +16377,7 @@
       <c r="I59" s="7"/>
       <c r="J59" s="7"/>
     </row>
-    <row r="60" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
         <v>6</v>
       </c>
@@ -16397,11 +16397,11 @@
         <v>62</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H60" s="5"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>6</v>
       </c>
@@ -16425,7 +16425,7 @@
       <c r="I61" s="7"/>
       <c r="J61" s="7"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>6</v>
       </c>
@@ -16449,7 +16449,7 @@
       <c r="I62" s="7"/>
       <c r="J62" s="7"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>6</v>
       </c>
@@ -16473,7 +16473,7 @@
       <c r="I63" s="7"/>
       <c r="J63" s="7"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>6</v>
       </c>
@@ -16497,7 +16497,7 @@
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>6</v>
       </c>
@@ -16521,7 +16521,7 @@
       <c r="I65" s="7"/>
       <c r="J65" s="7"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>6</v>
       </c>
@@ -16545,7 +16545,7 @@
       <c r="I66" s="7"/>
       <c r="J66" s="7"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>6</v>
       </c>
@@ -16569,7 +16569,7 @@
       <c r="I67" s="7"/>
       <c r="J67" s="7"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>6</v>
       </c>
@@ -16593,7 +16593,7 @@
       <c r="I68" s="7"/>
       <c r="J68" s="7"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>6</v>
       </c>
@@ -16613,11 +16613,11 @@
         <v>71</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H69" s="5"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>6</v>
       </c>
@@ -16641,7 +16641,7 @@
       <c r="I70" s="7"/>
       <c r="J70" s="7"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>6</v>
       </c>
@@ -16665,7 +16665,7 @@
       <c r="I71" s="7"/>
       <c r="J71" s="7"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>6</v>
       </c>
@@ -16689,7 +16689,7 @@
       <c r="I72" s="7"/>
       <c r="J72" s="7"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>6</v>
       </c>
@@ -16713,7 +16713,7 @@
       <c r="I73" s="7"/>
       <c r="J73" s="7"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>6</v>
       </c>
@@ -16737,7 +16737,7 @@
       <c r="I74" s="7"/>
       <c r="J74" s="7"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>6</v>
       </c>
@@ -16761,7 +16761,7 @@
       <c r="I75" s="7"/>
       <c r="J75" s="7"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>6</v>
       </c>
@@ -16785,7 +16785,7 @@
       <c r="I76" s="7"/>
       <c r="J76" s="7"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>6</v>
       </c>
@@ -16809,7 +16809,7 @@
       <c r="I77" s="7"/>
       <c r="J77" s="7"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>6</v>
       </c>
@@ -16833,7 +16833,7 @@
       <c r="I78" s="7"/>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>6</v>
       </c>
@@ -16853,11 +16853,11 @@
         <v>81</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>6</v>
       </c>
@@ -16881,7 +16881,7 @@
       <c r="I80" s="7"/>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>6</v>
       </c>
@@ -16905,7 +16905,7 @@
       <c r="I81" s="7"/>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>6</v>
       </c>
@@ -16929,7 +16929,7 @@
       <c r="I82" s="7"/>
       <c r="J82" s="7"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>6</v>
       </c>
@@ -16953,7 +16953,7 @@
       <c r="I83" s="7"/>
       <c r="J83" s="7"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>6</v>
       </c>
@@ -16977,7 +16977,7 @@
       <c r="I84" s="7"/>
       <c r="J84" s="7"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>6</v>
       </c>
@@ -17001,7 +17001,7 @@
       <c r="I85" s="7"/>
       <c r="J85" s="7"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>6</v>
       </c>
@@ -17025,7 +17025,7 @@
       <c r="I86" s="7"/>
       <c r="J86" s="7"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>6</v>
       </c>
@@ -17049,7 +17049,7 @@
       <c r="I87" s="7"/>
       <c r="J87" s="7"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>6</v>
       </c>
@@ -17073,7 +17073,7 @@
       <c r="I88" s="7"/>
       <c r="J88" s="7"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>6</v>
       </c>
@@ -17097,7 +17097,7 @@
       <c r="I89" s="7"/>
       <c r="J89" s="7"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>6</v>
       </c>
@@ -17121,7 +17121,7 @@
       <c r="I90" s="7"/>
       <c r="J90" s="7"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>6</v>
       </c>
@@ -17145,7 +17145,7 @@
       <c r="I91" s="7"/>
       <c r="J91" s="7"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>6</v>
       </c>
@@ -17169,7 +17169,7 @@
       <c r="I92" s="7"/>
       <c r="J92" s="7"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>6</v>
       </c>
@@ -17193,7 +17193,7 @@
       <c r="I93" s="7"/>
       <c r="J93" s="7"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>6</v>
       </c>
@@ -17217,7 +17217,7 @@
       <c r="I94" s="7"/>
       <c r="J94" s="7"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>6</v>
       </c>
@@ -17241,7 +17241,7 @@
       <c r="I95" s="7"/>
       <c r="J95" s="7"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>6</v>
       </c>
@@ -17265,7 +17265,7 @@
       <c r="I96" s="7"/>
       <c r="J96" s="7"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>6</v>
       </c>
@@ -17289,7 +17289,7 @@
       <c r="I97" s="7"/>
       <c r="J97" s="7"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>6</v>
       </c>
@@ -17313,7 +17313,7 @@
       <c r="I98" s="7"/>
       <c r="J98" s="7"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>6</v>
       </c>
@@ -17337,7 +17337,7 @@
       <c r="I99" s="7"/>
       <c r="J99" s="7"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>6</v>
       </c>
@@ -17361,7 +17361,7 @@
       <c r="I100" s="7"/>
       <c r="J100" s="7"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>6</v>
       </c>
@@ -17385,7 +17385,7 @@
       <c r="I101" s="7"/>
       <c r="J101" s="7"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>6</v>
       </c>
@@ -17409,7 +17409,7 @@
       <c r="I102" s="7"/>
       <c r="J102" s="7"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>6</v>
       </c>
@@ -17433,7 +17433,7 @@
       <c r="I103" s="7"/>
       <c r="J103" s="7"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>6</v>
       </c>
@@ -17457,7 +17457,7 @@
       <c r="I104" s="7"/>
       <c r="J104" s="7"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>6</v>
       </c>
@@ -17481,7 +17481,7 @@
       <c r="I105" s="7"/>
       <c r="J105" s="7"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>6</v>
       </c>
@@ -17505,7 +17505,7 @@
       <c r="I106" s="7"/>
       <c r="J106" s="7"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>6</v>
       </c>
@@ -17529,7 +17529,7 @@
       <c r="I107" s="7"/>
       <c r="J107" s="7"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>6</v>
       </c>
@@ -17553,7 +17553,7 @@
       <c r="I108" s="7"/>
       <c r="J108" s="7"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>6</v>
       </c>
@@ -17577,7 +17577,7 @@
       <c r="I109" s="7"/>
       <c r="J109" s="7"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>6</v>
       </c>
@@ -17601,7 +17601,7 @@
       <c r="I110" s="7"/>
       <c r="J110" s="7"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>6</v>
       </c>
@@ -17625,7 +17625,7 @@
       <c r="I111" s="7"/>
       <c r="J111" s="7"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
         <v>6</v>
       </c>
@@ -17649,7 +17649,7 @@
       <c r="I112" s="7"/>
       <c r="J112" s="7"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
         <v>6</v>
       </c>
@@ -17673,7 +17673,7 @@
       <c r="I113" s="7"/>
       <c r="J113" s="7"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
         <v>6</v>
       </c>
@@ -17697,7 +17697,7 @@
       <c r="I114" s="7"/>
       <c r="J114" s="7"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
         <v>6</v>
       </c>
@@ -17721,7 +17721,7 @@
       <c r="I115" s="7"/>
       <c r="J115" s="7"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
         <v>6</v>
       </c>
@@ -17745,7 +17745,7 @@
       <c r="I116" s="7"/>
       <c r="J116" s="7"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
         <v>6</v>
       </c>
@@ -17769,7 +17769,7 @@
       <c r="I117" s="7"/>
       <c r="J117" s="7"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
         <v>6</v>
       </c>
@@ -17793,7 +17793,7 @@
       <c r="I118" s="7"/>
       <c r="J118" s="7"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
         <v>6</v>
       </c>
@@ -17817,7 +17817,7 @@
       <c r="I119" s="7"/>
       <c r="J119" s="7"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
         <v>6</v>
       </c>
@@ -17841,7 +17841,7 @@
       <c r="I120" s="7"/>
       <c r="J120" s="7"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
         <v>6</v>
       </c>
@@ -17865,7 +17865,7 @@
       <c r="I121" s="7"/>
       <c r="J121" s="7"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
         <v>6</v>
       </c>
@@ -17889,7 +17889,7 @@
       <c r="I122" s="7"/>
       <c r="J122" s="7"/>
     </row>
-    <row r="123" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
         <v>6</v>
       </c>
@@ -17909,11 +17909,11 @@
         <v>126</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H123" s="5"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
         <v>6</v>
       </c>
@@ -17937,7 +17937,7 @@
       <c r="I124" s="7"/>
       <c r="J124" s="7"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
         <v>6</v>
       </c>
@@ -17961,7 +17961,7 @@
       <c r="I125" s="7"/>
       <c r="J125" s="7"/>
     </row>
-    <row r="126" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
         <v>6</v>
       </c>
@@ -17981,11 +17981,11 @@
         <v>129</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H126" s="5"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
         <v>6</v>
       </c>
@@ -18009,7 +18009,7 @@
       <c r="I127" s="7"/>
       <c r="J127" s="7"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
         <v>6</v>
       </c>
@@ -18033,7 +18033,7 @@
       <c r="I128" s="7"/>
       <c r="J128" s="7"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
         <v>6</v>
       </c>
@@ -18057,7 +18057,7 @@
       <c r="I129" s="7"/>
       <c r="J129" s="7"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
         <v>6</v>
       </c>
@@ -18081,7 +18081,7 @@
       <c r="I130" s="7"/>
       <c r="J130" s="7"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
         <v>6</v>
       </c>
@@ -18105,7 +18105,7 @@
       <c r="I131" s="7"/>
       <c r="J131" s="7"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
         <v>6</v>
       </c>
@@ -18129,7 +18129,7 @@
       <c r="I132" s="7"/>
       <c r="J132" s="7"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
         <v>6</v>
       </c>
@@ -18153,7 +18153,7 @@
       <c r="I133" s="7"/>
       <c r="J133" s="7"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
         <v>6</v>
       </c>
@@ -18177,7 +18177,7 @@
       <c r="I134" s="7"/>
       <c r="J134" s="7"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
         <v>6</v>
       </c>
@@ -18201,7 +18201,7 @@
       <c r="I135" s="7"/>
       <c r="J135" s="7"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
         <v>6</v>
       </c>
@@ -18225,7 +18225,7 @@
       <c r="I136" s="7"/>
       <c r="J136" s="7"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
         <v>6</v>
       </c>
@@ -18249,7 +18249,7 @@
       <c r="I137" s="7"/>
       <c r="J137" s="7"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
         <v>6</v>
       </c>
@@ -18273,7 +18273,7 @@
       <c r="I138" s="7"/>
       <c r="J138" s="7"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>6</v>
       </c>
@@ -18297,7 +18297,7 @@
       <c r="I139" s="7"/>
       <c r="J139" s="7"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
         <v>6</v>
       </c>
@@ -18321,7 +18321,7 @@
       <c r="I140" s="7"/>
       <c r="J140" s="7"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
         <v>6</v>
       </c>
@@ -18345,7 +18345,7 @@
       <c r="I141" s="7"/>
       <c r="J141" s="7"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
         <v>6</v>
       </c>
@@ -18369,7 +18369,7 @@
       <c r="I142" s="7"/>
       <c r="J142" s="7"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
         <v>6</v>
       </c>
@@ -18393,7 +18393,7 @@
       <c r="I143" s="7"/>
       <c r="J143" s="7"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
         <v>6</v>
       </c>
@@ -18417,7 +18417,7 @@
       <c r="I144" s="7"/>
       <c r="J144" s="7"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
         <v>6</v>
       </c>
@@ -18441,7 +18441,7 @@
       <c r="I145" s="7"/>
       <c r="J145" s="7"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
         <v>6</v>
       </c>
@@ -18465,7 +18465,7 @@
       <c r="I146" s="7"/>
       <c r="J146" s="7"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
         <v>6</v>
       </c>
@@ -18489,7 +18489,7 @@
       <c r="I147" s="7"/>
       <c r="J147" s="7"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
         <v>6</v>
       </c>
@@ -18513,7 +18513,7 @@
       <c r="I148" s="7"/>
       <c r="J148" s="7"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
         <v>6</v>
       </c>
@@ -18537,7 +18537,7 @@
       <c r="I149" s="7"/>
       <c r="J149" s="7"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
         <v>6</v>
       </c>
@@ -18561,7 +18561,7 @@
       <c r="I150" s="7"/>
       <c r="J150" s="7"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
         <v>6</v>
       </c>
@@ -18585,7 +18585,7 @@
       <c r="I151" s="7"/>
       <c r="J151" s="7"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
         <v>6</v>
       </c>
@@ -18609,7 +18609,7 @@
       <c r="I152" s="7"/>
       <c r="J152" s="7"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
         <v>6</v>
       </c>
@@ -18633,7 +18633,7 @@
       <c r="I153" s="7"/>
       <c r="J153" s="7"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
         <v>6</v>
       </c>
@@ -18657,7 +18657,7 @@
       <c r="I154" s="7"/>
       <c r="J154" s="7"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
         <v>6</v>
       </c>
@@ -18681,7 +18681,7 @@
       <c r="I155" s="7"/>
       <c r="J155" s="7"/>
     </row>
-    <row r="156" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A156" s="5" t="s">
         <v>6</v>
       </c>
@@ -18701,11 +18701,11 @@
         <v>160</v>
       </c>
       <c r="G156" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H156" s="5"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
         <v>6</v>
       </c>
@@ -18729,7 +18729,7 @@
       <c r="I157" s="7"/>
       <c r="J157" s="7"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
         <v>6</v>
       </c>
@@ -18753,7 +18753,7 @@
       <c r="I158" s="7"/>
       <c r="J158" s="7"/>
     </row>
-    <row r="159" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A159" s="5" t="s">
         <v>6</v>
       </c>
@@ -18773,11 +18773,11 @@
         <v>163</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H159" s="5"/>
     </row>
-    <row r="160" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A160" s="5" t="s">
         <v>6</v>
       </c>
@@ -18797,11 +18797,11 @@
         <v>164</v>
       </c>
       <c r="G160" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H160" s="5"/>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
         <v>6</v>
       </c>
@@ -18825,7 +18825,7 @@
       <c r="I161" s="7"/>
       <c r="J161" s="7"/>
     </row>
-    <row r="162" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A162" s="5" t="s">
         <v>6</v>
       </c>
@@ -18845,11 +18845,11 @@
         <v>166</v>
       </c>
       <c r="G162" s="9" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H162" s="5"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
         <v>6</v>
       </c>
@@ -18872,12 +18872,12 @@
         <v>394</v>
       </c>
       <c r="H163" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I163" s="7"/>
       <c r="J163" s="7"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
         <v>6</v>
       </c>
@@ -18903,7 +18903,7 @@
       <c r="I164" s="7"/>
       <c r="J164" s="7"/>
     </row>
-    <row r="165" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A165" s="5" t="s">
         <v>6</v>
       </c>
@@ -18923,11 +18923,11 @@
         <v>169</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H165" s="5"/>
     </row>
-    <row r="166" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A166" s="5" t="s">
         <v>6</v>
       </c>
@@ -18959,18 +18959,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CDE0891-8AA6-4E97-8DD7-0A40EF8B98BE}">
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -18990,13 +18990,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -19018,7 +19018,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -19040,7 +19040,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -19062,7 +19062,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
@@ -19082,13 +19082,13 @@
         <v>4</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5"/>
       <c r="J5"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -19110,7 +19110,7 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -19132,7 +19132,7 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -19154,7 +19154,7 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
@@ -19176,7 +19176,7 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
@@ -19198,7 +19198,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
@@ -19220,7 +19220,7 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>6</v>
       </c>
@@ -19240,13 +19240,13 @@
         <v>11</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12"/>
       <c r="J12"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>6</v>
       </c>
@@ -19268,7 +19268,7 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>6</v>
       </c>
@@ -19290,7 +19290,7 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>6</v>
       </c>
@@ -19310,13 +19310,13 @@
         <v>14</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15"/>
       <c r="J15"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>6</v>
       </c>
@@ -19338,7 +19338,7 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>6</v>
       </c>
@@ -19358,13 +19358,13 @@
         <v>16</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17"/>
       <c r="J17"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
@@ -19386,7 +19386,7 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -19408,7 +19408,7 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>6</v>
       </c>
@@ -19428,13 +19428,13 @@
         <v>19</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20"/>
       <c r="J20"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>6</v>
       </c>
@@ -19456,7 +19456,7 @@
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>6</v>
       </c>
@@ -19478,7 +19478,7 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>6</v>
       </c>
@@ -19498,13 +19498,13 @@
         <v>22</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23"/>
       <c r="J23"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>6</v>
       </c>
@@ -19526,7 +19526,7 @@
       <c r="G24" s="11"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>6</v>
       </c>
@@ -19548,7 +19548,7 @@
       <c r="G25" s="11"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>6</v>
       </c>
@@ -19568,13 +19568,13 @@
         <v>25</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26"/>
       <c r="J26"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>6</v>
       </c>
@@ -19596,7 +19596,7 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>6</v>
       </c>
@@ -19618,7 +19618,7 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>6</v>
       </c>
@@ -19638,13 +19638,13 @@
         <v>28</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H29" s="5"/>
       <c r="I29"/>
       <c r="J29"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -19666,7 +19666,7 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -19688,7 +19688,7 @@
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>6</v>
       </c>
@@ -19708,13 +19708,13 @@
         <v>31</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32"/>
       <c r="J32"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>6</v>
       </c>
@@ -19734,11 +19734,11 @@
         <v>32</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>6</v>
       </c>
@@ -19758,11 +19758,11 @@
         <v>33</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>6</v>
       </c>
@@ -19782,7 +19782,7 @@
         <v>34</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35"/>
@@ -19796,18 +19796,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2052FE1-3645-4163-A812-B0012D742164}">
   <dimension ref="A1:J38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="62" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -19827,13 +19827,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -19855,7 +19855,7 @@
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -19877,7 +19877,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -19899,7 +19899,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
@@ -19919,11 +19919,11 @@
         <v>4</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -19947,7 +19947,7 @@
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -19971,7 +19971,7 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -19995,7 +19995,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
@@ -20019,7 +20019,7 @@
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
@@ -20043,7 +20043,7 @@
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
@@ -20067,7 +20067,7 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>6</v>
       </c>
@@ -20087,11 +20087,11 @@
         <v>11</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>6</v>
       </c>
@@ -20115,7 +20115,7 @@
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>6</v>
       </c>
@@ -20139,7 +20139,7 @@
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>6</v>
       </c>
@@ -20159,11 +20159,11 @@
         <v>14</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>6</v>
       </c>
@@ -20187,7 +20187,7 @@
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>6</v>
       </c>
@@ -20207,11 +20207,11 @@
         <v>16</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
@@ -20235,7 +20235,7 @@
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -20259,7 +20259,7 @@
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
     </row>
-    <row r="20" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>6</v>
       </c>
@@ -20279,11 +20279,11 @@
         <v>19</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>6</v>
       </c>
@@ -20307,7 +20307,7 @@
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>6</v>
       </c>
@@ -20331,7 +20331,7 @@
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>6</v>
       </c>
@@ -20351,11 +20351,11 @@
         <v>22</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>6</v>
       </c>
@@ -20379,7 +20379,7 @@
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>6</v>
       </c>
@@ -20403,7 +20403,7 @@
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>6</v>
       </c>
@@ -20423,11 +20423,11 @@
         <v>25</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>6</v>
       </c>
@@ -20451,7 +20451,7 @@
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>6</v>
       </c>
@@ -20475,7 +20475,7 @@
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>6</v>
       </c>
@@ -20495,11 +20495,11 @@
         <v>28</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -20523,7 +20523,7 @@
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -20547,7 +20547,7 @@
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>6</v>
       </c>
@@ -20567,11 +20567,11 @@
         <v>31</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H32" s="5"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>6</v>
       </c>
@@ -20595,7 +20595,7 @@
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>6</v>
       </c>
@@ -20619,7 +20619,7 @@
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>6</v>
       </c>
@@ -20639,11 +20639,11 @@
         <v>34</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H35" s="5"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>6</v>
       </c>
@@ -20663,13 +20663,13 @@
         <v>35</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>6</v>
       </c>
@@ -20689,13 +20689,13 @@
         <v>36</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
     </row>
-    <row r="38" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>6</v>
       </c>
@@ -20715,7 +20715,7 @@
         <v>37</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H38" s="5"/>
     </row>
